--- a/table/Datas/#DodgeStage.xlsx
+++ b/table/Datas/#DodgeStage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>interval_seconds</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>caption</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +504,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,6 +516,11 @@
           <t>##group</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -546,6 +561,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>interval_seconds</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>caption</t>
         </is>
       </c>
     </row>
@@ -555,7 +575,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>탄막</t>
+          <t>슬리퍼</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -574,6 +594,11 @@
       </c>
       <c r="H5" t="n">
         <v>1.8</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>슬리퍼가 날아듭니다. 선수들, 발끝에 집중합니다.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -582,7 +607,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>폭탄</t>
+          <t>수박</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -601,6 +626,11 @@
       </c>
       <c r="H6" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>하늘에서 수박이 떨어집니다. 그림자를 보십시오.</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -609,7 +639,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>레이저</t>
+          <t>줄넘기</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -628,6 +658,11 @@
       </c>
       <c r="H7" t="n">
         <v>1.5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>줄넘기 구간입니다. 거인 형제가 입장합니다.</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -636,7 +671,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>바위</t>
+          <t>장독</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -655,6 +690,11 @@
       </c>
       <c r="H8" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>장독이 굴러옵니다. 벽 쪽이 위험합니다.</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -663,7 +703,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>바닥</t>
+          <t>온돌</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -682,6 +722,11 @@
       </c>
       <c r="H9" t="n">
         <v>1.6</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>바닥이 달아오릅니다. 선수들, 바닥을 읽습니다.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#DodgeStage.xlsx
+++ b/table/Datas/#DodgeStage.xlsx
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="n">
         <v>0.5</v>
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="n">
         <v>1.5</v>
@@ -683,10 +683,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
         <v>1.6</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
         <v>0.6</v>

--- a/table/Datas/#DodgeStage.xlsx
+++ b/table/Datas/#DodgeStage.xlsx
@@ -583,11 +583,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>8,9,2,3</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="G5" t="n">
         <v>0.5</v>

--- a/table/Datas/#DodgeStage.xlsx
+++ b/table/Datas/#DodgeStage.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8,9,2,3</t>
+          <t>8,9,3</t>
         </is>
       </c>
       <c r="F5" t="n">

--- a/table/Datas/#DodgeStage.xlsx
+++ b/table/Datas/#DodgeStage.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H5" t="n">
         <v>1.8</v>
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H6" t="n">
         <v>1.6</v>
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="n">
         <v>1.5</v>
@@ -683,10 +683,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
         <v>1.6</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
         <v>1.6</v>
